--- a/artfynd/A 63804-2025 artfynd.xlsx
+++ b/artfynd/A 63804-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 63804-2025 artfynd.xlsx
+++ b/artfynd/A 63804-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129178796</v>
+        <v>129178837</v>
       </c>
       <c r="B2" t="n">
-        <v>58100</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129178792</v>
+        <v>129178796</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129178837</v>
+        <v>129179158</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619341</v>
+        <v>619301</v>
       </c>
       <c r="R4" t="n">
-        <v>6878903</v>
+        <v>6879066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129179158</v>
+        <v>129178792</v>
       </c>
       <c r="B5" t="n">
-        <v>57890</v>
+        <v>58085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>205976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619301</v>
+        <v>619341</v>
       </c>
       <c r="R5" t="n">
-        <v>6879066</v>
+        <v>6878903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,6 +1076,240 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129178862</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Muggberget, Muggberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>619341</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6878903</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129179229</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Muggberget, Bäling, Jättendal, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>619181</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6878926</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Växer på undersida av tallåga</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Växer på undersida av tallåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63804-2025 artfynd.xlsx
+++ b/artfynd/A 63804-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129178837</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129178796</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129179158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129178792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129178862</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,8 +1340,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129179229</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>